--- a/Sajat_telephely_Gyar.xlsx
+++ b/Sajat_telephely_Gyar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\vizsgához\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E1333E9-D8BB-428D-BD44-2BBC1DDA0633}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0538861C-936C-4783-80C8-6CDC90355813}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" xr2:uid="{367F2E2F-EFD4-4A7E-979A-BF8BDBF0F12D}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="66">
   <si>
     <t>Darabszámok</t>
   </si>
@@ -75,9 +75,6 @@
     <t xml:space="preserve">24 db </t>
   </si>
   <si>
-    <t>5 db</t>
-  </si>
-  <si>
     <t>20 db</t>
   </si>
   <si>
@@ -96,14 +93,143 @@
     <t>Acces point</t>
   </si>
   <si>
-    <t>14 db</t>
+    <t>15 db</t>
+  </si>
+  <si>
+    <t>Vlan kiosztás</t>
+  </si>
+  <si>
+    <t>Vlan</t>
+  </si>
+  <si>
+    <t>Név</t>
+  </si>
+  <si>
+    <t>Hálózat</t>
+  </si>
+  <si>
+    <t>IRODA</t>
+  </si>
+  <si>
+    <t>GYARTAS</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>GUEST</t>
+  </si>
+  <si>
+    <t>SERVER</t>
+  </si>
+  <si>
+    <t>MANAGEMENT</t>
+  </si>
+  <si>
+    <t>10.0.8.0/24</t>
+  </si>
+  <si>
+    <t>10.0.9.0/24</t>
+  </si>
+  <si>
+    <t>10.0.12.0/24</t>
+  </si>
+  <si>
+    <t>10.0.13.0/24</t>
+  </si>
+  <si>
+    <t>10.0.11.0/24</t>
+  </si>
+  <si>
+    <t>10.0.10.0/24</t>
+  </si>
+  <si>
+    <t>IPv4 kiosztás</t>
+  </si>
+  <si>
+    <t>Ipv4 cím</t>
+  </si>
+  <si>
+    <t>IPv6 kiosztás</t>
+  </si>
+  <si>
+    <t>IPv6 cím</t>
+  </si>
+  <si>
+    <t>Költségek</t>
+  </si>
+  <si>
+    <t>Ár</t>
+  </si>
+  <si>
+    <t>Kábelek</t>
+  </si>
+  <si>
+    <t>Típus</t>
+  </si>
+  <si>
+    <t>Funkció</t>
+  </si>
+  <si>
+    <t>Szabvány</t>
+  </si>
+  <si>
+    <t>Elhelyezkedés</t>
+  </si>
+  <si>
+    <t>Hossz/mennyiség</t>
+  </si>
+  <si>
+    <t>Cat6 réz</t>
+  </si>
+  <si>
+    <t>Optikai</t>
+  </si>
+  <si>
+    <t>Wi-Fi AP</t>
+  </si>
+  <si>
+    <t>LAN kapcsolat munkaállomásokhoz, irodai eszközökhöz</t>
+  </si>
+  <si>
+    <t>Telephelyi és telephelyek közötti összeköttetés</t>
+  </si>
+  <si>
+    <t>Mobil eszközök, roaming(mobiltelefon-szolgáltatások külföldi használata )</t>
+  </si>
+  <si>
+    <t>Cat6</t>
+  </si>
+  <si>
+    <t>--</t>
+  </si>
+  <si>
+    <t>ipari AP-k</t>
+  </si>
+  <si>
+    <t>Kábelcsatorna, mennyezeti tálca</t>
+  </si>
+  <si>
+    <t>Függőleges és backbone összeköttetés</t>
+  </si>
+  <si>
+    <t>Gyártótér, admin, raktár</t>
+  </si>
+  <si>
+    <t>Több száz méter (2500 m² csarnok)</t>
+  </si>
+  <si>
+    <t>Nem részletezett, igény szerint</t>
+  </si>
+  <si>
+    <t>16 db különböző területen</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -143,8 +269,22 @@
       <family val="1"/>
       <charset val="238"/>
     </font>
+    <font>
+      <sz val="26"/>
+      <color theme="0"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <sz val="28"/>
+      <color theme="0"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="238"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -160,6 +300,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.59996337778862885"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -228,7 +386,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -237,14 +395,50 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -559,115 +753,284 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B51A87EB-994D-4F56-AC3C-6B1C70EF786E}">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:Y13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="54.28515625" customWidth="1"/>
     <col min="2" max="2" width="13.5703125" customWidth="1"/>
+    <col min="4" max="4" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="30.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="30.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="69.28515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="36" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="31.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" ht="35.25" x14ac:dyDescent="0.5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
+      <c r="D1" s="5" t="s">
+        <v>23</v>
+      </c>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
-    </row>
-    <row r="2" spans="1:6" ht="21" x14ac:dyDescent="0.25">
+      <c r="I1" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q1" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="U1" s="19"/>
+      <c r="V1" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" ht="21" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="4" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+      <c r="D2" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q2" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="R2" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="U2" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="V2" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="W2" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="X2" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y2" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="7">
+        <v>10</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="U3" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="V3" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="W3" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="X3" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y3" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="6" t="s">
+      <c r="D4" s="7">
+        <v>20</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="U4" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="V4" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="W4" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="X4" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y4" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="7">
+        <v>30</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="U5" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="V5" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="W5" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="X5" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y5" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="7">
+        <v>40</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="7">
+        <v>50</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="7">
+        <v>99</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="11"/>
+    </row>
+    <row r="12" spans="1:25" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="12" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="6"/>
-    </row>
-    <row r="12" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
+      <c r="B13" s="13" t="s">
         <v>22</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>
